--- a/public/downloads/BackPrediction2018.xlsx
+++ b/public/downloads/BackPrediction2018.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,10 +169,31 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>O</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>HO</t>
+  </si>
+  <si>
+    <t>O</t>
   </si>
   <si>
     <t>HO2</t>
@@ -659,10 +682,10 @@
         <v>67</v>
       </c>
       <c r="N3" s="5">
-        <v>451.5427043437958</v>
+        <v>451542.7043437958</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03119250513565873</v>
+        <v>31.19250513565873</v>
       </c>
       <c r="P3" s="5">
         <v>14476</v>
@@ -709,10 +732,10 @@
         <v>67</v>
       </c>
       <c r="N4" s="5">
-        <v>702.2179112434387</v>
+        <v>702217.9112434387</v>
       </c>
       <c r="O4" s="4">
-        <v>0.05970225397410633</v>
+        <v>59.70225397410633</v>
       </c>
       <c r="P4" s="5">
         <v>11762</v>
@@ -759,10 +782,10 @@
         <v>67</v>
       </c>
       <c r="N5" s="5">
-        <v>1612.06206035614</v>
+        <v>1612062.06035614</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1451654264165817</v>
+        <v>145.1654264165817</v>
       </c>
       <c r="P5" s="5">
         <v>11105</v>
@@ -809,10 +832,10 @@
         <v>67</v>
       </c>
       <c r="N6" s="5">
-        <v>1134.978584289551</v>
+        <v>1134978.584289551</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08746752345018116</v>
+        <v>87.46752345018116</v>
       </c>
       <c r="P6" s="5">
         <v>12976</v>
@@ -859,10 +882,10 @@
         <v>67</v>
       </c>
       <c r="N7" s="5">
-        <v>2093.128367424011</v>
+        <v>2093128.367424011</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2264555195741655</v>
+        <v>226.4555195741655</v>
       </c>
       <c r="P7" s="5">
         <v>9243</v>
@@ -909,10 +932,10 @@
         <v>67</v>
       </c>
       <c r="N8" s="5">
-        <v>196.0508630275726</v>
+        <v>196050.8630275726</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01617714852938135</v>
+        <v>16.17714852938135</v>
       </c>
       <c r="P8" s="5">
         <v>12119</v>
@@ -959,10 +982,10 @@
         <v>67</v>
       </c>
       <c r="N9" s="5">
-        <v>690.6929850578308</v>
+        <v>690692.9850578308</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03120083954726615</v>
+        <v>31.20083954726615</v>
       </c>
       <c r="P9" s="5">
         <v>22137</v>
@@ -1009,10 +1032,10 @@
         <v>67</v>
       </c>
       <c r="N10" s="5">
-        <v>931.3412461280823</v>
+        <v>931341.2461280823</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08721240248413543</v>
+        <v>87.21240248413544</v>
       </c>
       <c r="P10" s="5">
         <v>10679</v>
@@ -1059,10 +1082,10 @@
         <v>67</v>
       </c>
       <c r="N11" s="5">
-        <v>556.3016932010651</v>
+        <v>556301.6932010651</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04235262224598896</v>
+        <v>42.35262224598897</v>
       </c>
       <c r="P11" s="5">
         <v>13135</v>
@@ -1109,10 +1132,10 @@
         <v>67</v>
       </c>
       <c r="N12" s="5">
-        <v>221.4271330833435</v>
+        <v>221427.1330833435</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02124001276578835</v>
+        <v>21.24001276578835</v>
       </c>
       <c r="P12" s="5">
         <v>10425</v>
@@ -1159,10 +1182,10 @@
         <v>67</v>
       </c>
       <c r="N13" s="5">
-        <v>990.6326549053192</v>
+        <v>990632.6549053192</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07761145839120333</v>
+        <v>77.61145839120333</v>
       </c>
       <c r="P13" s="5">
         <v>12764</v>
@@ -1209,10 +1232,10 @@
         <v>67</v>
       </c>
       <c r="N14" s="5">
-        <v>6460.900545120239</v>
+        <v>6460900.545120239</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3138797388806956</v>
+        <v>313.8797388806956</v>
       </c>
       <c r="P14" s="5">
         <v>20584</v>
@@ -1259,10 +1282,10 @@
         <v>67</v>
       </c>
       <c r="N15" s="5">
-        <v>3390.348572254181</v>
+        <v>3390348.572254181</v>
       </c>
       <c r="O15" s="4">
-        <v>0.3180141236520196</v>
+        <v>318.0141236520196</v>
       </c>
       <c r="P15" s="5">
         <v>10661</v>
@@ -1309,10 +1332,10 @@
         <v>67</v>
       </c>
       <c r="N16" s="5">
-        <v>2108.629929542542</v>
+        <v>2108629.929542542</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1002629418259969</v>
+        <v>100.2629418259969</v>
       </c>
       <c r="P16" s="5">
         <v>21031</v>
@@ -1359,10 +1382,10 @@
         <v>67</v>
       </c>
       <c r="N17" s="5">
-        <v>1155.152983665466</v>
+        <v>1155152.983665466</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1000392295544701</v>
+        <v>100.0392295544701</v>
       </c>
       <c r="P17" s="5">
         <v>11547</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,25 +1497,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1463342033664224</v>
+        <v>0.1855216044547504</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1399276038129307</v>
+        <v>0.1317648904929124</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1164879724146164</v>
+        <v>0.1101642245868364</v>
       </c>
       <c r="E3" s="4">
-        <v>85.74829931972759</v>
+        <v>84.01064773735564</v>
       </c>
       <c r="F3" s="4">
-        <v>84.57348506954604</v>
+        <v>81.79311351036068</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
@@ -1487,105 +1542,159 @@
         <v>18</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.0107393975791952</v>
+      </c>
+      <c r="O3" s="5">
+        <v>18</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1841208134661597</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.130571624095224</v>
+      </c>
+      <c r="R3" s="5">
+        <v>18</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2150606142928012</v>
+        <v>0.1352180658894347</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1471529940208181</v>
+        <v>0.1015014487836464</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1198532423816476</v>
+        <v>0.1248462384238794</v>
       </c>
       <c r="E4" s="4">
-        <v>84.50458444247211</v>
+        <v>85.29724933451641</v>
       </c>
       <c r="F4" s="4">
-        <v>83.82258535162099</v>
+        <v>83.65042311059193</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.02079253233861742</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1379301353249066</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1015014487836464</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1305747489809247</v>
+        <v>0.242906598024807</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1051676551763892</v>
+        <v>0.1971126850082925</v>
       </c>
       <c r="D5" s="4">
-        <v>0.09772370618424747</v>
+        <v>0.185983462399106</v>
       </c>
       <c r="E5" s="4">
-        <v>84.16099773242603</v>
+        <v>81.86264982183353</v>
       </c>
       <c r="F5" s="4">
-        <v>78.70725471396636</v>
+        <v>74.04602109300149</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
       </c>
       <c r="H5" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="5">
         <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1365826790998373</v>
+      </c>
+      <c r="O5" s="5">
+        <v>14</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2303534821118077</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1490152941888283</v>
+      </c>
+      <c r="R5" s="5">
+        <v>14</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,132 +1797,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2126814356809373</v>
+        <v>0.3476869672353967</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1803116234206641</v>
+        <v>0.2707624031607201</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1503975354208772</v>
+        <v>0.289035550523653</v>
       </c>
       <c r="E3" s="4">
-        <v>80.20556048506332</v>
+        <v>67.34250221827914</v>
       </c>
       <c r="F3" s="4">
-        <v>81.036377784263</v>
+        <v>71.56453652368381</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2396444712980681</v>
+      </c>
+      <c r="O3" s="5">
+        <v>17</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3300799907068148</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.218747732410513</v>
+      </c>
+      <c r="R3" s="5">
+        <v>17</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2633693166236402</v>
+        <v>2044.836559019886</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1790184474885099</v>
+        <v>0.3411405935441943</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1446900232275885</v>
+        <v>0.4520917684266185</v>
       </c>
       <c r="E4" s="4">
-        <v>78.75628512274419</v>
+        <v>68.10411120970066</v>
       </c>
       <c r="F4" s="4">
-        <v>80.62348020620639</v>
+        <v>73.19035113315982</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I4" s="5">
         <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.243874580925052</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2044.794773430239</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2770693560843711</v>
+      </c>
+      <c r="R4" s="5">
+        <v>15</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1953815511838516</v>
+        <v>350.3121166146831</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1714066090822213</v>
+        <v>0.5732636866778572</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1552313853584852</v>
+        <v>0.7152544170179183</v>
       </c>
       <c r="E5" s="4">
-        <v>77.77129899578867</v>
+        <v>66.52575315840578</v>
       </c>
       <c r="F5" s="4">
-        <v>72.9018855864481</v>
+        <v>69.75018642803737</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
       </c>
       <c r="H5" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="5">
         <v>5</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.5732636866778572</v>
+      </c>
+      <c r="O5" s="5">
+        <v>12</v>
+      </c>
+      <c r="P5" s="4">
+        <v>350.0471231367067</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2228914186621122</v>
+      </c>
+      <c r="R5" s="5">
+        <v>12</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,132 +2097,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1768215944699989</v>
+        <v>0.2150606142928012</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1710397017407198</v>
+        <v>0.1471529940208181</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1703833175486162</v>
+        <v>0.1198532423816476</v>
       </c>
       <c r="E3" s="4">
-        <v>86.96983141082517</v>
+        <v>84.50458444247211</v>
       </c>
       <c r="F3" s="4">
-        <v>85.16438089680035</v>
+        <v>83.82258535162099</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.0150817925596789</v>
+      </c>
+      <c r="O3" s="5">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2130934239589301</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1471529940208181</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2519278690145197</v>
+        <v>0.1463342033664224</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1521252856396504</v>
+        <v>0.1399276038129307</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1513627936955464</v>
+        <v>0.1164879724146164</v>
       </c>
       <c r="E4" s="4">
-        <v>85.06211180124153</v>
+        <v>85.74829931972759</v>
       </c>
       <c r="F4" s="4">
-        <v>83.00894854586289</v>
+        <v>84.57348506954604</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.0714605162455947</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1347323653202791</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1132581965734096</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2658158643104765</v>
+        <v>0.1305747489809247</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1725800748426371</v>
+        <v>0.1051676551763892</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2049394119264997</v>
+        <v>0.09772370618424747</v>
       </c>
       <c r="E5" s="4">
-        <v>84.90281827016524</v>
+        <v>84.16099773242603</v>
       </c>
       <c r="F5" s="4">
-        <v>78.97997230212097</v>
+        <v>78.70725471396636</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
       </c>
       <c r="H5" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I5" s="5">
         <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.0336435267184952</v>
+      </c>
+      <c r="O5" s="5">
+        <v>13</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.128808466599478</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1023144297909754</v>
+      </c>
+      <c r="R5" s="5">
+        <v>13</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,25 +2397,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1726490439570969</v>
+        <v>0.2633693166236402</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1685899035539665</v>
+        <v>0.1790184474885099</v>
       </c>
       <c r="D3" s="4">
-        <v>0.119523326110263</v>
+        <v>0.1446900232275885</v>
       </c>
       <c r="E3" s="4">
-        <v>84.77965099083109</v>
+        <v>78.75628512274419</v>
       </c>
       <c r="F3" s="4">
-        <v>83.0074895438206</v>
+        <v>80.62348020620639</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
@@ -2140,91 +2456,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.00953833784236187</v>
+      </c>
+      <c r="O3" s="5">
+        <v>17</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2644902802714322</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1794128879717153</v>
+      </c>
+      <c r="R3" s="5">
+        <v>17</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3669081517880658</v>
+        <v>0.2126814356809373</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3041227756985957</v>
+        <v>0.1803116234206641</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2970298110804591</v>
+        <v>0.1503975354208772</v>
       </c>
       <c r="E4" s="4">
-        <v>81.24815143448619</v>
+        <v>80.20556048506332</v>
       </c>
       <c r="F4" s="4">
-        <v>78.17381577667584</v>
+        <v>81.036377784263</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.02967044469507803</v>
+      </c>
+      <c r="O4" s="5">
+        <v>19</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2067639517448497</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1762715580975137</v>
+      </c>
+      <c r="R4" s="5">
+        <v>19</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3675989294812514</v>
+        <v>0.1953815511838516</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3087565001204335</v>
+        <v>0.1714066090822213</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2559123599439826</v>
+        <v>0.1552313853584852</v>
       </c>
       <c r="E5" s="4">
-        <v>79.68091998704253</v>
+        <v>77.77129899578867</v>
       </c>
       <c r="F5" s="4">
-        <v>68.90327048045232</v>
+        <v>72.9018855864481</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
       </c>
       <c r="H5" s="5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.001456251728711777</v>
+      </c>
+      <c r="O5" s="5">
+        <v>13</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1954508965042664</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1712945897184743</v>
+      </c>
+      <c r="R5" s="5">
+        <v>13</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2697,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.042592784340725</v>
+        <v>0.2519278690145197</v>
       </c>
       <c r="C3" s="4">
-        <v>1.151615068688436</v>
+        <v>0.1521252856396504</v>
       </c>
       <c r="D3" s="4">
-        <v>0.970778017282148</v>
+        <v>0.1513627936955464</v>
       </c>
       <c r="E3" s="4">
-        <v>46.63856847086661</v>
+        <v>85.06211180124153</v>
       </c>
       <c r="F3" s="4">
-        <v>53.81529034140718</v>
+        <v>83.00894854586289</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1209072197753951</v>
+      </c>
+      <c r="O3" s="5">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2147053671492815</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.129547983105466</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4103394972514506</v>
+        <v>0.1768215944699989</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5415831215623351</v>
+        <v>0.1710397017407198</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4360457833965021</v>
+        <v>0.1703833175486162</v>
       </c>
       <c r="E4" s="4">
-        <v>46.17420881396028</v>
+        <v>86.96983141082517</v>
       </c>
       <c r="F4" s="4">
-        <v>55.56463379048737</v>
+        <v>85.16438089680035</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1261192774747744</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1694796189280467</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1515050593344923</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.471548044478462</v>
+        <v>0.2658158643104765</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6474223811597586</v>
+        <v>0.1725800748426371</v>
       </c>
       <c r="D5" s="4">
-        <v>0.541422221689822</v>
+        <v>0.2049394119264997</v>
       </c>
       <c r="E5" s="4">
-        <v>44.29219306770314</v>
+        <v>84.90281827016524</v>
       </c>
       <c r="F5" s="4">
-        <v>53.23053158623606</v>
+        <v>78.97997230212097</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
       </c>
       <c r="H5" s="5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1356148443938578</v>
+      </c>
+      <c r="O5" s="5">
+        <v>11</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2197334623312367</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.13683634408897</v>
+      </c>
+      <c r="R5" s="5">
+        <v>11</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,66 +2997,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4102348604535527</v>
+        <v>0.3669081517880658</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4097994338639952</v>
+        <v>0.3041227756985957</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3445839592325142</v>
+        <v>0.2970298110804591</v>
       </c>
       <c r="E3" s="4">
-        <v>88.2165039929011</v>
+        <v>81.24815143448619</v>
       </c>
       <c r="F3" s="4">
-        <v>85.80877346561816</v>
+        <v>78.17381577667584</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2871804093251354</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1946771937071783</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1742573262906601</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5385794364253881</v>
+        <v>0.1726490439570969</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4548289090024711</v>
+        <v>0.1685899035539665</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4108310364525256</v>
+        <v>0.119523326110263</v>
       </c>
       <c r="E4" s="4">
-        <v>85.23809523809501</v>
+        <v>84.77965099083109</v>
       </c>
       <c r="F4" s="4">
-        <v>81.49450442563871</v>
+        <v>83.0074895438206</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
@@ -2593,64 +3101,100 @@
         <v>17</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1327618238653205</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1914106555712599</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1627351842401117</v>
+      </c>
+      <c r="R4" s="5">
+        <v>17</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7739416904831392</v>
+        <v>0.3675989294812514</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7087210025188313</v>
+        <v>0.3087565001204335</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6257752156413332</v>
+        <v>0.2559123599439826</v>
       </c>
       <c r="E5" s="4">
-        <v>83.36086815678625</v>
+        <v>79.68091998704253</v>
       </c>
       <c r="F5" s="4">
-        <v>72.5854905720675</v>
+        <v>68.90327048045232</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
       </c>
       <c r="H5" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
         <v>4</v>
       </c>
       <c r="J5" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.3071923690152924</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2209158457607802</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2098257316536329</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,25 +3297,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8071915996782448</v>
+        <v>0.4103394972514506</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8102078473307023</v>
+        <v>0.5415831215623351</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8696819018339129</v>
+        <v>0.4360457833965021</v>
       </c>
       <c r="E3" s="4">
-        <v>46.04111209701266</v>
+        <v>46.17420881396028</v>
       </c>
       <c r="F3" s="4">
-        <v>53.91401614628956</v>
+        <v>55.56463379048737</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
@@ -2771,99 +3348,151 @@
         <v>17</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.5235458884240435</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4073562466210399</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2612828103310865</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.411008353264772</v>
+        <v>1.042592784340725</v>
       </c>
       <c r="C4" s="4">
-        <v>0.419260113275921</v>
+        <v>1.151615068688436</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3750611909145909</v>
+        <v>0.970778017282148</v>
       </c>
       <c r="E4" s="4">
-        <v>46.02188701567594</v>
+        <v>46.63856847086661</v>
       </c>
       <c r="F4" s="4">
-        <v>53.97772590215025</v>
+        <v>53.81529034140718</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-1.361584365397158</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6631541127471016</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3710761309566624</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4911996446504354</v>
+        <v>0.471548044478462</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5717588571204253</v>
+        <v>0.6474223811597586</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4924856254219093</v>
+        <v>0.541422221689822</v>
       </c>
       <c r="E5" s="4">
-        <v>44.58373825720751</v>
+        <v>44.29219306770314</v>
       </c>
       <c r="F5" s="4">
-        <v>52.08479812506684</v>
+        <v>53.23053158623606</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
       </c>
       <c r="H5" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.471548044478462</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6474223811597586</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3503,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3511,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3522,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3564,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,116 +3595,170 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3247331768992049</v>
+        <v>0.5385794364253881</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3387002991863363</v>
+        <v>0.4548289090024711</v>
       </c>
       <c r="D3" s="4">
-        <v>0.319156273969641</v>
+        <v>0.4108310364525256</v>
       </c>
       <c r="E3" s="4">
-        <v>81.17568766637076</v>
+        <v>85.23809523809501</v>
       </c>
       <c r="F3" s="4">
-        <v>83.21466783386821</v>
+        <v>81.49450442563871</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4548289090024711</v>
+      </c>
+      <c r="O3" s="5">
+        <v>17</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1697205315853294</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.095892895148531</v>
+      </c>
+      <c r="R3" s="5">
+        <v>17</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3153423948794644</v>
+        <v>0.4102348604535527</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2967897618791605</v>
+        <v>0.4097994338639952</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2945407327764489</v>
+        <v>0.3445839592325142</v>
       </c>
       <c r="E4" s="4">
-        <v>81.88701567583506</v>
+        <v>88.2165039929011</v>
       </c>
       <c r="F4" s="4">
-        <v>81.01060208150989</v>
+        <v>85.80877346561816</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4037478566403478</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1380002379133874</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1266425125016826</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4816720036253043</v>
+        <v>0.7739416904831392</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4774534277585551</v>
+        <v>0.7087210025188313</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4524910724318528</v>
+        <v>0.6257752156413332</v>
       </c>
       <c r="E5" s="4">
-        <v>79.72303206997051</v>
+        <v>83.36086815678625</v>
       </c>
       <c r="F5" s="4">
-        <v>75.07297326089122</v>
+        <v>72.5854905720675</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
       </c>
       <c r="H5" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="5">
         <v>7</v>
@@ -3074,9 +3772,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.7087210025188313</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2023216854032919</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08111997821158497</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3803,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.411008353264772</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.419260113275921</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3750611909145909</v>
+      </c>
+      <c r="E3" s="4">
+        <v>46.02188701567594</v>
+      </c>
+      <c r="F3" s="4">
+        <v>53.97772590215025</v>
+      </c>
+      <c r="G3" s="5">
+        <v>23</v>
+      </c>
+      <c r="H3" s="5">
+        <v>7</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>16</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>16</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3655701324418723</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4565592011308151</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2565674448934186</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.8071915996782448</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.8102078473307023</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.8696819018339129</v>
+      </c>
+      <c r="E4" s="4">
+        <v>46.04111209701266</v>
+      </c>
+      <c r="F4" s="4">
+        <v>53.91401614628956</v>
+      </c>
+      <c r="G4" s="5">
+        <v>23</v>
+      </c>
+      <c r="H4" s="5">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>17</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>15</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.9953052557780379</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5815635165580008</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4450435179838924</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4911996446504354</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.5717588571204253</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4924856254219093</v>
+      </c>
+      <c r="E5" s="4">
+        <v>44.58373825720751</v>
+      </c>
+      <c r="F5" s="4">
+        <v>52.08479812506684</v>
+      </c>
+      <c r="G5" s="5">
+        <v>21</v>
+      </c>
+      <c r="H5" s="5">
+        <v>6</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>15</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>14</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.4002493155430891</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5281433319135053</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3328553287826589</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3153423948794644</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2967897618791605</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2945407327764489</v>
+      </c>
+      <c r="E3" s="4">
+        <v>81.88701567583506</v>
+      </c>
+      <c r="F3" s="4">
+        <v>81.01060208150989</v>
+      </c>
+      <c r="G3" s="5">
+        <v>23</v>
+      </c>
+      <c r="H3" s="5">
+        <v>17</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>6</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>6</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2967897618791605</v>
+      </c>
+      <c r="O3" s="5">
+        <v>17</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.131704530347341</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.120286989594077</v>
+      </c>
+      <c r="R3" s="5">
+        <v>17</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3247331768992049</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3387002991863363</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.319156273969641</v>
+      </c>
+      <c r="E4" s="4">
+        <v>81.17568766637076</v>
+      </c>
+      <c r="F4" s="4">
+        <v>83.21466783386821</v>
+      </c>
+      <c r="G4" s="5">
+        <v>23</v>
+      </c>
+      <c r="H4" s="5">
+        <v>18</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>5</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3387002991863363</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1813148479012965</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1590164245951493</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4816720036253043</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.4774534277585551</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4524910724318528</v>
+      </c>
+      <c r="E5" s="4">
+        <v>79.72303206997051</v>
+      </c>
+      <c r="F5" s="4">
+        <v>75.07297326089122</v>
+      </c>
+      <c r="G5" s="5">
+        <v>21</v>
+      </c>
+      <c r="H5" s="5">
+        <v>11</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>7</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>7</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.4774534277585551</v>
+      </c>
+      <c r="O5" s="5">
+        <v>11</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1766392998927955</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.200428176649425</v>
+      </c>
+      <c r="R5" s="5">
+        <v>11</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>52.23880597014925</v>
+      </c>
+      <c r="C3" s="3">
+        <v>5.970149253731343</v>
+      </c>
+      <c r="D3" s="3">
+        <v>41.7910447761194</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>41.7910447761194</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.2624726967510381</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2165649422511302</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.186867986099266</v>
+      </c>
+      <c r="K3" s="4">
+        <v>77.50583815615813</v>
+      </c>
+      <c r="L3" s="4">
+        <v>73.7415272630147</v>
+      </c>
+      <c r="M3" s="5">
+        <v>67</v>
+      </c>
+      <c r="N3" s="5">
+        <v>451542.7043437958</v>
+      </c>
+      <c r="O3" s="4">
+        <v>31.19250513565873</v>
+      </c>
+      <c r="P3" s="5">
+        <v>14476</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>82.08955223880598</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2.985074626865671</v>
+      </c>
+      <c r="D4" s="3">
+        <v>14.92537313432836</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>14.92537313432836</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.3086914181187472</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2799244266814636</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2768141905110604</v>
+      </c>
+      <c r="K4" s="4">
+        <v>82.89978678038401</v>
+      </c>
+      <c r="L4" s="4">
+        <v>82.39306821596814</v>
+      </c>
+      <c r="M4" s="5">
+        <v>67</v>
+      </c>
+      <c r="N4" s="5">
+        <v>702217.9112434387</v>
+      </c>
+      <c r="O4" s="4">
+        <v>59.70225397410633</v>
+      </c>
+      <c r="P4" s="5">
+        <v>11762</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>82.08955223880598</v>
+      </c>
+      <c r="C5" s="3">
+        <v>4.477611940298507</v>
+      </c>
+      <c r="D5" s="3">
+        <v>13.43283582089552</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>13.43283582089552</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.1666882116583919</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1443195031595771</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1218678796330866</v>
+      </c>
+      <c r="K5" s="4">
+        <v>84.66900192912981</v>
+      </c>
+      <c r="L5" s="4">
+        <v>83.92884570436465</v>
+      </c>
+      <c r="M5" s="5">
+        <v>67</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1612062.06035614</v>
+      </c>
+      <c r="O5" s="4">
+        <v>145.1654264165817</v>
+      </c>
+      <c r="P5" s="5">
+        <v>11105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>70.14925373134329</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5.970149253731343</v>
+      </c>
+      <c r="D6" s="3">
+        <v>23.88059701492537</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>23.88059701492537</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.263348109385669</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2123634644782824</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2033477912778604</v>
+      </c>
+      <c r="K6" s="4">
+        <v>80.39597928723749</v>
+      </c>
+      <c r="L6" s="4">
+        <v>78.77174530034421</v>
+      </c>
+      <c r="M6" s="5">
+        <v>67</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1134978.584289551</v>
+      </c>
+      <c r="O6" s="4">
+        <v>87.46752345018116</v>
+      </c>
+      <c r="P6" s="5">
+        <v>12976</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>86.56716417910447</v>
+      </c>
+      <c r="C7" s="3">
+        <v>5.970149253731343</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7.462686567164178</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>7.462686567164178</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.130727015466179</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1253264419785549</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.07766815134810136</v>
+      </c>
+      <c r="K7" s="4">
+        <v>89.30805157884096</v>
+      </c>
+      <c r="L7" s="4">
+        <v>87.2399746235275</v>
+      </c>
+      <c r="M7" s="5">
+        <v>67</v>
+      </c>
+      <c r="N7" s="5">
+        <v>2093128.367424011</v>
+      </c>
+      <c r="O7" s="4">
+        <v>226.4555195741655</v>
+      </c>
+      <c r="P7" s="5">
+        <v>9243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>77.61194029850746</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4.477611940298507</v>
+      </c>
+      <c r="D8" s="3">
+        <v>17.91044776119403</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>17.91044776119403</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.1827551484558579</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1243563909236646</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1205974544447218</v>
+      </c>
+      <c r="K8" s="4">
+        <v>83.77906386435184</v>
+      </c>
+      <c r="L8" s="4">
+        <v>80.00250425723759</v>
+      </c>
+      <c r="M8" s="5">
+        <v>67</v>
+      </c>
+      <c r="N8" s="5">
+        <v>196050.8630275726</v>
+      </c>
+      <c r="O8" s="4">
+        <v>16.17714852938135</v>
+      </c>
+      <c r="P8" s="5">
+        <v>12119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>65.67164179104478</v>
+      </c>
+      <c r="C9" s="3">
+        <v>8.955223880597014</v>
+      </c>
+      <c r="D9" s="3">
+        <v>25.37313432835821</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5.970149253731343</v>
+      </c>
+      <c r="F9" s="3">
+        <v>19.40298507462687</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>811.7740479783968</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.2397602003679462</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.2763131017337599</v>
+      </c>
+      <c r="K9" s="4">
+        <v>67.34795410701594</v>
+      </c>
+      <c r="L9" s="4">
+        <v>71.55397509099011</v>
+      </c>
+      <c r="M9" s="5">
+        <v>67</v>
+      </c>
+      <c r="N9" s="5">
+        <v>690692.9850578308</v>
+      </c>
+      <c r="O9" s="4">
+        <v>31.20083954726615</v>
+      </c>
+      <c r="P9" s="5">
+        <v>22137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>70.14925373134329</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2.985074626865671</v>
+      </c>
+      <c r="D10" s="3">
+        <v>26.86567164179105</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>26.86567164179105</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1597756858509082</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1217698517007903</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1043272645705206</v>
+      </c>
+      <c r="K10" s="4">
+        <v>84.82383998375495</v>
+      </c>
+      <c r="L10" s="4">
+        <v>82.47704430865868</v>
+      </c>
+      <c r="M10" s="5">
+        <v>67</v>
+      </c>
+      <c r="N10" s="5">
+        <v>931341.2461280823</v>
+      </c>
+      <c r="O10" s="4">
+        <v>87.21240248413544</v>
+      </c>
+      <c r="P10" s="5">
+        <v>10679</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>73.13432835820896</v>
+      </c>
+      <c r="C11" s="3">
+        <v>5.970149253731343</v>
+      </c>
+      <c r="D11" s="3">
+        <v>20.8955223880597</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>20.8955223880597</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2230345695964788</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1760409870553487</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1489148781643803</v>
+      </c>
+      <c r="K11" s="4">
+        <v>78.94507056553967</v>
+      </c>
+      <c r="L11" s="4">
+        <v>78.34501986710831</v>
+      </c>
+      <c r="M11" s="5">
+        <v>67</v>
+      </c>
+      <c r="N11" s="5">
+        <v>556301.6932010651</v>
+      </c>
+      <c r="O11" s="4">
+        <v>42.35262224598897</v>
+      </c>
+      <c r="P11" s="5">
+        <v>13135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>67.16417910447761</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2.985074626865671</v>
+      </c>
+      <c r="D12" s="3">
+        <v>29.85074626865671</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>29.85074626865671</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2007560804288734</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1401124129485997</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1413788841058315</v>
+      </c>
+      <c r="K12" s="4">
+        <v>85.66707279926923</v>
+      </c>
+      <c r="L12" s="4">
+        <v>82.48605963471311</v>
+      </c>
+      <c r="M12" s="5">
+        <v>67</v>
+      </c>
+      <c r="N12" s="5">
+        <v>221427.1330833435</v>
+      </c>
+      <c r="O12" s="4">
+        <v>21.24001276578835</v>
+      </c>
+      <c r="P12" s="5">
+        <v>10425</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>55.22388059701493</v>
+      </c>
+      <c r="C13" s="3">
+        <v>10.44776119402985</v>
+      </c>
+      <c r="D13" s="3">
+        <v>34.32835820895522</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>34.32835820895522</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.2017798999161263</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1747312186506199</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1420075503666771</v>
+      </c>
+      <c r="K13" s="4">
+        <v>81.96923545537621</v>
+      </c>
+      <c r="L13" s="4">
+        <v>76.92744332031263</v>
+      </c>
+      <c r="M13" s="5">
+        <v>67</v>
+      </c>
+      <c r="N13" s="5">
+        <v>990632.6549053192</v>
+      </c>
+      <c r="O13" s="4">
+        <v>77.61145839120333</v>
+      </c>
+      <c r="P13" s="5">
+        <v>12764</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>22.38805970149254</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>77.61194029850746</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1.492537313432836</v>
+      </c>
+      <c r="F14" s="3">
+        <v>76.11940298507463</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.5152872716345516</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.4008511360939244</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.5309076580303437</v>
+      </c>
+      <c r="K14" s="4">
+        <v>45.74373032795201</v>
+      </c>
+      <c r="L14" s="4">
+        <v>54.23252863200675</v>
+      </c>
+      <c r="M14" s="5">
+        <v>67</v>
+      </c>
+      <c r="N14" s="5">
+        <v>6460900.545120239</v>
+      </c>
+      <c r="O14" s="4">
+        <v>313.8797388806956</v>
+      </c>
+      <c r="P14" s="5">
+        <v>20584</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>67.16417910447761</v>
+      </c>
+      <c r="C15" s="3">
+        <v>5.970149253731343</v>
+      </c>
+      <c r="D15" s="3">
+        <v>26.86567164179105</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>26.86567164179105</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1690497476408898</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1049098716593592</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.09279023133341491</v>
+      </c>
+      <c r="K15" s="4">
+        <v>85.67214945679802</v>
+      </c>
+      <c r="L15" s="4">
+        <v>80.18314467928927</v>
+      </c>
+      <c r="M15" s="5">
+        <v>67</v>
+      </c>
+      <c r="N15" s="5">
+        <v>3390348.572254181</v>
+      </c>
+      <c r="O15" s="4">
+        <v>318.0141236520196</v>
+      </c>
+      <c r="P15" s="5">
+        <v>10661</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>29.85074626865671</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>70.14925373134329</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.985074626865671</v>
+      </c>
+      <c r="F16" s="3">
+        <v>67.16417910447761</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.5219079474183042</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.3454204356418565</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.4758495328636753</v>
+      </c>
+      <c r="K16" s="4">
+        <v>45.57772362676429</v>
+      </c>
+      <c r="L16" s="4">
+        <v>53.36254966776811</v>
+      </c>
+      <c r="M16" s="5">
+        <v>67</v>
+      </c>
+      <c r="N16" s="5">
+        <v>2108629.929542542</v>
+      </c>
+      <c r="O16" s="4">
+        <v>100.2629418259969</v>
+      </c>
+      <c r="P16" s="5">
+        <v>21031</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>68.65671641791045</v>
+      </c>
+      <c r="C17" s="3">
+        <v>4.477611940298507</v>
+      </c>
+      <c r="D17" s="3">
+        <v>26.86567164179105</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>26.86567164179105</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.1628189701114533</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1546061828033842</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1379505913356681</v>
+      </c>
+      <c r="K17" s="4">
+        <v>80.96456493045</v>
+      </c>
+      <c r="L17" s="4">
+        <v>79.90617382884311</v>
+      </c>
+      <c r="M17" s="5">
+        <v>67</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1155152.983665466</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100.0392295544701</v>
+      </c>
+      <c r="P17" s="5">
+        <v>11547</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3470,16 +5644,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
+        <v>7</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
         <v>11</v>
-      </c>
-      <c r="M9" s="5">
-        <v>0</v>
-      </c>
-      <c r="N9" s="5">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3693,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
@@ -3778,16 +5952,16 @@
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3847,9 +6021,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>35</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5">
+        <v>28</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>28</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>15</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>55</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>10</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>55</v>
+      </c>
+      <c r="C5" s="5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>9</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>6</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>47</v>
+      </c>
+      <c r="C6" s="5">
+        <v>4</v>
+      </c>
+      <c r="D6" s="5">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>16</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>4</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>58</v>
+      </c>
+      <c r="C7" s="5">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5">
+        <v>5</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>5</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>3</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>52</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5">
+        <v>12</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>12</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>6</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>44</v>
+      </c>
+      <c r="C9" s="5">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5">
+        <v>4</v>
+      </c>
+      <c r="F9" s="5">
+        <v>13</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5">
+        <v>4</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>7</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>47</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>18</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>18</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>8</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>49</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5">
+        <v>14</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>14</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>6</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>45</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5">
+        <v>20</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>20</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>8</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>37</v>
+      </c>
+      <c r="C13" s="5">
+        <v>7</v>
+      </c>
+      <c r="D13" s="5">
+        <v>23</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>23</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>11</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>15</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>52</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5">
+        <v>51</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5">
+        <v>1</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>35</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>45</v>
+      </c>
+      <c r="C15" s="5">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5">
+        <v>18</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>18</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>11</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>20</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>47</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2</v>
+      </c>
+      <c r="F16" s="5">
+        <v>45</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>2</v>
+      </c>
+      <c r="I16" s="5">
+        <v>2</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>31</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3</v>
+      </c>
+      <c r="D17" s="5">
+        <v>18</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>18</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>5</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6789,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6831,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,25 +6862,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2819203376395849</v>
+        <v>0.3110924162384292</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2469591479037884</v>
+        <v>0.2534202915992491</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2350155143769615</v>
+        <v>0.1990895251082931</v>
       </c>
       <c r="E3" s="4">
-        <v>78.9988169180715</v>
+        <v>78.44128955930152</v>
       </c>
       <c r="F3" s="4">
-        <v>77.04843886781502</v>
+        <v>77.09853127127923</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
@@ -3960,25 +6921,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.07862433259437498</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3185897934277586</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2440923621749798</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3110924162384292</v>
+        <v>0.2819203376395849</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2534202915992491</v>
+        <v>0.2469591479037884</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1990895251082931</v>
+        <v>0.2350155143769615</v>
       </c>
       <c r="E4" s="4">
-        <v>78.44128955930152</v>
+        <v>78.9988169180715</v>
       </c>
       <c r="F4" s="4">
-        <v>77.09853127127923</v>
+        <v>77.04843886781502</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
@@ -4001,10 +6980,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1739838982302351</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2593933287170191</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2238006636376431</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.2593818390590118</v>
@@ -4042,9 +7039,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3419501729412064</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2043837558566507</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1470386596304054</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7070,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7089,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7131,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,92 +7162,146 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2492118749904413</v>
+        <v>0.3044210021876023</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2471622987194763</v>
+        <v>0.2625078718301516</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2451368063546548</v>
+        <v>0.2272107499771743</v>
       </c>
       <c r="E3" s="4">
-        <v>84.36853002070399</v>
+        <v>82.59834368529974</v>
       </c>
       <c r="F3" s="4">
-        <v>85.16681256687083</v>
+        <v>83.95389553545574</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1159442738616546</v>
+      </c>
+      <c r="O3" s="5">
+        <v>19</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3094620575728917</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2564055416269067</v>
+      </c>
+      <c r="R3" s="5">
+        <v>19</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3044210021876023</v>
+        <v>0.2492118749904413</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2625078718301516</v>
+        <v>0.2471622987194763</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2272107499771743</v>
+        <v>0.2451368063546548</v>
       </c>
       <c r="E4" s="4">
-        <v>82.59834368529974</v>
+        <v>84.36853002070399</v>
       </c>
       <c r="F4" s="4">
-        <v>83.95389553545574</v>
+        <v>85.16681256687083</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1379614190397916</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2110123589268503</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2101309261983363</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>1.648155379393377</v>
@@ -4255,9 +7339,27 @@
       <c r="M5" s="5">
         <v>5</v>
       </c>
+      <c r="N5" s="4">
+        <v>1.722019154369821</v>
+      </c>
+      <c r="O5" s="5">
+        <v>16</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4148292111648571</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3950949782876592</v>
+      </c>
+      <c r="R5" s="5">
+        <v>16</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7370,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7389,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7431,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,34 +7462,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.146009005823498</v>
+        <v>0.186316954977762</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1217863539209832</v>
+        <v>0.1720020494275346</v>
       </c>
       <c r="D3" s="4">
-        <v>0.09897274718514752</v>
+        <v>0.1394420988063614</v>
       </c>
       <c r="E3" s="4">
-        <v>84.745637385389</v>
+        <v>85.27950310559004</v>
       </c>
       <c r="F3" s="4">
-        <v>83.97918490419281</v>
+        <v>85.88415523781705</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>3</v>
@@ -4386,34 +7521,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.03398548247647711</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1820519969853787</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1721951701077653</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.186316954977762</v>
+        <v>0.146009005823498</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1720020494275346</v>
+        <v>0.1217863539209832</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1394420988063614</v>
+        <v>0.09897274718514752</v>
       </c>
       <c r="E4" s="4">
-        <v>85.27950310559004</v>
+        <v>84.745637385389</v>
       </c>
       <c r="F4" s="4">
-        <v>85.88415523781705</v>
+        <v>83.97918490419281</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
@@ -4427,10 +7580,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.01280720057910401</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1429507994354012</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1171671346151315</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1818020011434885</v>
@@ -4468,9 +7639,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.04047013527458469</v>
+      </c>
+      <c r="O5" s="5">
+        <v>17</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1758593268302057</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.14027416756171</v>
+      </c>
+      <c r="R5" s="5">
+        <v>17</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7670,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7689,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7731,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,92 +7762,146 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2447732245396881</v>
+        <v>0.2837228128401708</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2171102731178078</v>
+        <v>0.1901853928648002</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2393773618386947</v>
+        <v>0.1499450434425853</v>
       </c>
       <c r="E3" s="4">
-        <v>82.59686483288964</v>
+        <v>80.18929310854708</v>
       </c>
       <c r="F3" s="4">
-        <v>83.63145608403832</v>
+        <v>80.9332749732537</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.05112909684508375</v>
+      </c>
+      <c r="O3" s="5">
+        <v>17</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2903918254721382</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1931929867968639</v>
+      </c>
+      <c r="R3" s="5">
+        <v>17</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2837228128401708</v>
+        <v>0.2447732245396881</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1901853928648002</v>
+        <v>0.2171102731178078</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1499450434425853</v>
+        <v>0.2393773618386947</v>
       </c>
       <c r="E4" s="4">
-        <v>80.18929310854708</v>
+        <v>82.59686483288964</v>
       </c>
       <c r="F4" s="4">
-        <v>80.9332749732537</v>
+        <v>83.63145608403832</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.03630198133205593</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2404232492315805</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2216358550385747</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.2566523668008006</v>
@@ -4681,9 +7939,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.02578375031800799</v>
+      </c>
+      <c r="O5" s="5">
+        <v>12</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2588369814597283</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2256130553531868</v>
+      </c>
+      <c r="R5" s="5">
+        <v>12</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7970,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7989,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8031,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,92 +8062,146 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1333369339415949</v>
+        <v>0.1344161421796951</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1335423907448595</v>
+        <v>0.1305562164913632</v>
       </c>
       <c r="D3" s="4">
-        <v>0.08507245560642712</v>
+        <v>0.08767512667157254</v>
       </c>
       <c r="E3" s="4">
-        <v>89.42324755989307</v>
+        <v>90.45696539485309</v>
       </c>
       <c r="F3" s="4">
-        <v>88.26378756930164</v>
+        <v>89.94650325844025</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.05975699281128367</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1267793535232664</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1252885280237915</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1344161421796951</v>
+        <v>0.1333369339415949</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1305562164913632</v>
+        <v>0.1335423907448595</v>
       </c>
       <c r="D4" s="4">
-        <v>0.08767512667157254</v>
+        <v>0.08507245560642712</v>
       </c>
       <c r="E4" s="4">
-        <v>90.45696539485309</v>
+        <v>89.42324755989307</v>
       </c>
       <c r="F4" s="4">
-        <v>89.94650325844025</v>
+        <v>88.26378756930164</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.07958369198184116</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1299827963118711</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1315868502370331</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1404039114355961</v>
@@ -4894,9 +8239,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.05303856095661862</v>
+      </c>
+      <c r="O5" s="5">
+        <v>15</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1358657423821825</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1166174775503386</v>
+      </c>
+      <c r="R5" s="5">
+        <v>15</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8270,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.1352180658894347</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1015014487836464</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1248462384238794</v>
-      </c>
-      <c r="E3" s="4">
-        <v>85.29724933451641</v>
-      </c>
-      <c r="F3" s="4">
-        <v>83.65042311059193</v>
-      </c>
-      <c r="G3" s="5">
-        <v>23</v>
-      </c>
-      <c r="H3" s="5">
-        <v>20</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>3</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1855216044547504</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1317648904929124</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1101642245868364</v>
-      </c>
-      <c r="E4" s="4">
-        <v>84.01064773735564</v>
-      </c>
-      <c r="F4" s="4">
-        <v>81.79311351036068</v>
-      </c>
-      <c r="G4" s="5">
-        <v>23</v>
-      </c>
-      <c r="H4" s="5">
-        <v>18</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>4</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>4</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.242906598024807</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1971126850082925</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.185983462399106</v>
-      </c>
-      <c r="E5" s="4">
-        <v>81.86264982183353</v>
-      </c>
-      <c r="F5" s="4">
-        <v>74.04602109300149</v>
-      </c>
-      <c r="G5" s="5">
-        <v>21</v>
-      </c>
-      <c r="H5" s="5">
-        <v>14</v>
-      </c>
-      <c r="I5" s="5">
-        <v>2</v>
-      </c>
-      <c r="J5" s="5">
-        <v>5</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>5</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>2044.836559019886</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3411405935441943</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4520917684266185</v>
-      </c>
-      <c r="E3" s="4">
-        <v>68.10411120970066</v>
-      </c>
-      <c r="F3" s="4">
-        <v>73.19035113315982</v>
-      </c>
-      <c r="G3" s="5">
-        <v>23</v>
-      </c>
-      <c r="H3" s="5">
-        <v>15</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>7</v>
-      </c>
-      <c r="K3" s="5">
-        <v>3</v>
-      </c>
-      <c r="L3" s="5">
-        <v>4</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3476869672353967</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2707624031607201</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.289035550523653</v>
-      </c>
-      <c r="E4" s="4">
-        <v>67.34250221827914</v>
-      </c>
-      <c r="F4" s="4">
-        <v>71.56453652368381</v>
-      </c>
-      <c r="G4" s="5">
-        <v>23</v>
-      </c>
-      <c r="H4" s="5">
-        <v>17</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>5</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>5</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>350.3121166146831</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.5732636866778572</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.7152544170179183</v>
-      </c>
-      <c r="E5" s="4">
-        <v>66.52575315840578</v>
-      </c>
-      <c r="F5" s="4">
-        <v>69.75018642803737</v>
-      </c>
-      <c r="G5" s="5">
-        <v>21</v>
-      </c>
-      <c r="H5" s="5">
-        <v>12</v>
-      </c>
-      <c r="I5" s="5">
-        <v>4</v>
-      </c>
-      <c r="J5" s="5">
-        <v>5</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>4</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/BackPrediction2018.xlsx
+++ b/public/downloads/BackPrediction2018.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0107393975791952</v>
+        <v>-0.03267720749200009</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1841208134661597</v>
+        <v>0.1823446264499141</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.130571624095224</v>
+        <v>0.1295208190140661</v>
       </c>
       <c r="R3" s="5">
         <v>18</v>
@@ -1616,13 +1616,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.02079253233861742</v>
+        <v>-0.01133097439356234</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1379301353249066</v>
+        <v>0.1366960190712037</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1015014487836464</v>
@@ -1675,13 +1675,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1365826790998373</v>
+        <v>0.1677580101050964</v>
       </c>
       <c r="O5" s="5">
         <v>14</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2303534821118077</v>
+        <v>0.2348071008268447</v>
       </c>
       <c r="Q5" s="4">
         <v>0.1490152941888283</v>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2396444712980681</v>
+        <v>0.170826705592674</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3300799907068148</v>
+        <v>0.3211037603974156</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.218747732410513</v>
+        <v>0.2146996285454898</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.243874580925052</v>
+        <v>0.2293167338000615</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>2044.794773430239</v>
+        <v>2044.794140480363</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2770693560843711</v>
+        <v>0.276098832942705</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5732636866778572</v>
+        <v>0.512226368513808</v>
       </c>
       <c r="O5" s="5">
         <v>12</v>
       </c>
       <c r="P5" s="4">
-        <v>350.0471231367067</v>
+        <v>350.0327854808435</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2228914186621122</v>
+        <v>0.2130598504427089</v>
       </c>
       <c r="R5" s="5">
         <v>12</v>
@@ -2157,13 +2157,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0150817925596789</v>
+        <v>-0.0228789311779849</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2130934239589301</v>
+        <v>0.2120764058782814</v>
       </c>
       <c r="Q3" s="4">
         <v>0.1471529940208181</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.0714605162455947</v>
+        <v>-0.1011290490240384</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1347323653202791</v>
+        <v>0.1338948333540497</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1132581965734096</v>
+        <v>0.1072432613757092</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.0336435267184952</v>
+        <v>0.03381629465650349</v>
       </c>
       <c r="O5" s="5">
         <v>13</v>
       </c>
       <c r="P5" s="4">
-        <v>0.128808466599478</v>
+        <v>0.128800239554811</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1023144297909754</v>
+        <v>0.1023011399495902</v>
       </c>
       <c r="R5" s="5">
         <v>13</v>
@@ -2457,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.00953833784236187</v>
+        <v>0.002690188945337013</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2644902802714322</v>
+        <v>0.263486281360394</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1794128879717153</v>
+        <v>0.1788602010799607</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -2516,16 +2516,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.02967044469507803</v>
+        <v>0.02242033103760832</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2067639517448497</v>
+        <v>0.2070791740777832</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1762715580975137</v>
+        <v>0.1758899731681733</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.001456251728711777</v>
+        <v>0.02736995045165713</v>
       </c>
       <c r="O5" s="5">
         <v>13</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1954508965042664</v>
+        <v>0.19668488215774</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1712945897184743</v>
+        <v>0.1693012282782477</v>
       </c>
       <c r="R5" s="5">
         <v>13</v>
@@ -2757,13 +2757,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1209072197753951</v>
+        <v>-0.1005446389160056</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2147053671492815</v>
+        <v>0.2173613559570279</v>
       </c>
       <c r="Q3" s="4">
         <v>0.129547983105466</v>
@@ -2816,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1261192774747744</v>
+        <v>-0.110614643054177</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1694796189280467</v>
+        <v>0.1661887138637863</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1515050593344923</v>
+        <v>0.1498841197113702</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -2875,16 +2875,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1356148443938578</v>
+        <v>-0.1377268751928682</v>
       </c>
       <c r="O5" s="5">
         <v>11</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2197334623312367</v>
+        <v>0.2192305978552819</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.13683634408897</v>
+        <v>0.13664434128906</v>
       </c>
       <c r="R5" s="5">
         <v>11</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2871804093251354</v>
+        <v>-0.2718947336499014</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1946771937071783</v>
+        <v>0.1958858011200772</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1742573262906601</v>
+        <v>0.1742348159347123</v>
       </c>
       <c r="R3" s="5">
         <v>14</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1327618238653205</v>
+        <v>-0.06140105156978848</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1914106555712599</v>
+        <v>0.1727997032863473</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1627351842401117</v>
+        <v>0.1543464305124139</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -3175,13 +3175,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3071923690152924</v>
+        <v>-0.3137488138720812</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2209158457607802</v>
+        <v>0.2199792107812389</v>
       </c>
       <c r="Q5" s="4">
         <v>0.2098257316536329</v>
@@ -3357,13 +3357,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5235458884240435</v>
+        <v>-0.5784764864402661</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4073562466210399</v>
+        <v>0.438403975934557</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2612828103310865</v>
@@ -3416,16 +3416,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.361584365397158</v>
+        <v>-1.276838397310996</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6631541127471016</v>
+        <v>0.6299926469742556</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3710761309566624</v>
+        <v>0.35412693733943</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -3655,16 +3655,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4548289090024711</v>
+        <v>-0.4573613238886445</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1697205315853294</v>
+        <v>0.1693902166001763</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.095892895148531</v>
+        <v>0.09574392956699139</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -3714,16 +3714,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4037478566403478</v>
+        <v>-0.3973613933174374</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1380002379133874</v>
+        <v>0.1382085314553393</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1266425125016826</v>
+        <v>0.1265538618429039</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -3773,13 +3773,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7087210025188313</v>
+        <v>-0.7019663050477867</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2023216854032919</v>
+        <v>0.2026433376638178</v>
       </c>
       <c r="Q5" s="4">
         <v>0.08111997821158497</v>
@@ -3955,16 +3955,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3655701324418723</v>
+        <v>-0.5151687679913834</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4565592011308151</v>
+        <v>0.5333922178623511</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2565674448934186</v>
+        <v>0.2351962112434884</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -4014,16 +4014,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.9953052557780379</v>
+        <v>-0.9141019060982387</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5815635165580008</v>
+        <v>0.5529824990578677</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4450435179838924</v>
+        <v>0.4334430394582068</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -4073,16 +4073,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4002493155430891</v>
+        <v>-0.5938582220361788</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5281433319135053</v>
+        <v>0.6153448314414667</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3328553287826589</v>
+        <v>0.2763651916058916</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -4255,16 +4255,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2967897618791605</v>
+        <v>-0.322532020113897</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.131704530347341</v>
+        <v>0.1262878092634597</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.120286989594077</v>
+        <v>0.1156073463148466</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -4314,13 +4314,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3387002991863363</v>
+        <v>-0.3215406610565879</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1813148479012965</v>
+        <v>0.180568776678264</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1590164245951493</v>
@@ -4373,16 +4373,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4774534277585551</v>
+        <v>-0.4985593732444613</v>
       </c>
       <c r="O5" s="5">
         <v>11</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1766392998927955</v>
+        <v>0.1755838853507893</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.200428176649425</v>
+        <v>0.1985094543325245</v>
       </c>
       <c r="R5" s="5">
         <v>11</v>
@@ -4519,13 +4519,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.2624726967510381</v>
+        <v>0.2654435543778096</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2165649422511302</v>
+        <v>0.2123031105993635</v>
       </c>
       <c r="J3" s="4">
-        <v>0.186867986099266</v>
+        <v>0.1960682835533901</v>
       </c>
       <c r="K3" s="4">
         <v>77.50583815615813</v>
@@ -4569,13 +4569,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3086914181187472</v>
+        <v>0.3090207573615322</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2799244266814636</v>
+        <v>0.2786567633073053</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2768141905110604</v>
+        <v>0.2772980112309039</v>
       </c>
       <c r="K4" s="4">
         <v>82.89978678038401</v>
@@ -4619,13 +4619,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.1666882116583919</v>
+        <v>0.16906129912432</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1443195031595771</v>
+        <v>0.1426457322527943</v>
       </c>
       <c r="J5" s="4">
-        <v>0.1218678796330866</v>
+        <v>0.1240452381013258</v>
       </c>
       <c r="K5" s="4">
         <v>84.66900192912981</v>
@@ -4669,13 +4669,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.263348109385669</v>
+        <v>0.2635667117344884</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2123634644782824</v>
+        <v>0.2076050687516583</v>
       </c>
       <c r="J6" s="4">
-        <v>0.2033477912778604</v>
+        <v>0.2038685114320608</v>
       </c>
       <c r="K6" s="4">
         <v>80.39597928723749</v>
@@ -4719,13 +4719,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.130727015466179</v>
+        <v>0.1288128149556867</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1253264419785549</v>
+        <v>0.1216962255374434</v>
       </c>
       <c r="J7" s="4">
-        <v>0.07766815134810136</v>
+        <v>0.0738233174107928</v>
       </c>
       <c r="K7" s="4">
         <v>89.30805157884096</v>
@@ -4769,13 +4769,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.1827551484558579</v>
+        <v>0.1831176711096932</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1243563909236646</v>
+        <v>0.1239926507032637</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1205974544447218</v>
+        <v>0.1195673005474545</v>
       </c>
       <c r="K8" s="4">
         <v>83.77906386435184</v>
@@ -4819,13 +4819,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>811.7740479783968</v>
+        <v>811.7662554124657</v>
       </c>
       <c r="I9" s="4">
-        <v>0.2397602003679462</v>
+        <v>0.2351839632892365</v>
       </c>
       <c r="J9" s="4">
-        <v>0.2763131017337599</v>
+        <v>0.2800454876011488</v>
       </c>
       <c r="K9" s="4">
         <v>67.34795410701594</v>
@@ -4869,13 +4869,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1597756858509082</v>
+        <v>0.1591364706417111</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1217698517007903</v>
+        <v>0.119462583583841</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1043272645705206</v>
+        <v>0.1041462661662079</v>
       </c>
       <c r="K10" s="4">
         <v>84.82383998375495</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.2230345695964788</v>
+        <v>0.2231848955282182</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1760409870553487</v>
+        <v>0.1751724260443233</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1489148781643803</v>
+        <v>0.1471575564200606</v>
       </c>
       <c r="K11" s="4">
         <v>78.94507056553967</v>
@@ -4969,13 +4969,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2007560804288734</v>
+        <v>0.2003805098632783</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1401124129485997</v>
+        <v>0.1394171030815951</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1413788841058315</v>
+        <v>0.1403328848127749</v>
       </c>
       <c r="K12" s="4">
         <v>85.66707279926923</v>
@@ -5019,13 +5019,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.2017798999161263</v>
+        <v>0.195512388473937</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1747312186506199</v>
+        <v>0.1708684089653731</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1420075503666771</v>
+        <v>0.1373253411448958</v>
       </c>
       <c r="K13" s="4">
         <v>81.96923545537621</v>
@@ -5069,13 +5069,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.5152872716345516</v>
+        <v>0.5145616606111999</v>
       </c>
       <c r="I14" s="4">
-        <v>0.4008511360939244</v>
+        <v>0.3952014048881802</v>
       </c>
       <c r="J14" s="4">
-        <v>0.5309076580303437</v>
+        <v>0.5260125972725926</v>
       </c>
       <c r="K14" s="4">
         <v>45.74373032795201</v>
@@ -5119,13 +5119,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1690497476408898</v>
+        <v>0.1691086760629408</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1049098716593592</v>
+        <v>0.1048181355094883</v>
       </c>
       <c r="J15" s="4">
-        <v>0.09279023133341491</v>
+        <v>0.09124715200462581</v>
       </c>
       <c r="K15" s="4">
         <v>85.67214945679802</v>
@@ -5169,13 +5169,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.5219079474183042</v>
+        <v>0.5658038798423257</v>
       </c>
       <c r="I16" s="4">
-        <v>0.3454204356418565</v>
+        <v>0.3169332952273608</v>
       </c>
       <c r="J16" s="4">
-        <v>0.4758495328636753</v>
+        <v>0.5013792359020268</v>
       </c>
       <c r="K16" s="4">
         <v>45.57772362676429</v>
@@ -5219,13 +5219,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.1628189701114533</v>
+        <v>0.1603725831197943</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1546061828033842</v>
+        <v>0.1524179245157141</v>
       </c>
       <c r="J17" s="4">
-        <v>0.1379505913356681</v>
+        <v>0.1387001109289705</v>
       </c>
       <c r="K17" s="4">
         <v>80.96456493045</v>
@@ -6922,16 +6922,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.07862433259437498</v>
+        <v>0.129897746656809</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3185897934277586</v>
+        <v>0.3297361877891574</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2440923621749798</v>
+        <v>0.2440923621749797</v>
       </c>
       <c r="R3" s="5">
         <v>14</v>
@@ -6981,16 +6981,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1739838982302351</v>
+        <v>0.09798045307924497</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2593933287170191</v>
+        <v>0.2551877952427351</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2238006636376431</v>
+        <v>0.2137090510880841</v>
       </c>
       <c r="R4" s="5">
         <v>14</v>
@@ -7040,16 +7040,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3419501729412064</v>
+        <v>0.3498317050592163</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2043837558566507</v>
+        <v>0.2062603111228435</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1470386596304054</v>
+        <v>0.1459127264706897</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -7222,16 +7222,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1159442738616546</v>
+        <v>0.1491489731250226</v>
       </c>
       <c r="O3" s="5">
         <v>19</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3094620575728917</v>
+        <v>0.3109057401495598</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2564055416269067</v>
+        <v>0.254657925876203</v>
       </c>
       <c r="R3" s="5">
         <v>19</v>
@@ -7281,16 +7281,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1379614190397916</v>
+        <v>0.1258549937133751</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2110123589268503</v>
+        <v>0.2099510388838538</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2101309261983363</v>
+        <v>0.2083050868825694</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -7340,13 +7340,13 @@
         <v>5</v>
       </c>
       <c r="N5" s="4">
-        <v>1.722019154369821</v>
+        <v>1.726442951367204</v>
       </c>
       <c r="O5" s="5">
         <v>16</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4148292111648571</v>
+        <v>0.4154611821644832</v>
       </c>
       <c r="Q5" s="4">
         <v>0.3950949782876592</v>
@@ -7522,16 +7522,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.03398548247647711</v>
+        <v>-0.00911005492247341</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1820519969853787</v>
+        <v>0.1851286869443959</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1721951701077653</v>
+        <v>0.1720020494275346</v>
       </c>
       <c r="R3" s="5">
         <v>20</v>
@@ -7581,16 +7581,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.01280720057910401</v>
+        <v>0.03412614641936784</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1429507994354012</v>
+        <v>0.141729113238393</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1171671346151315</v>
+        <v>0.114421705261162</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -7640,16 +7640,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.04047013527458469</v>
+        <v>-0.001692877377593049</v>
       </c>
       <c r="O5" s="5">
         <v>17</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1758593268302057</v>
+        <v>0.1813989351012045</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.14027416756171</v>
+        <v>0.1379931523912988</v>
       </c>
       <c r="R5" s="5">
         <v>17</v>
@@ -7822,16 +7822,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.05112909684508375</v>
+        <v>-0.03941286319394521</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2903918254721382</v>
+        <v>0.2785820045974822</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1931929867968639</v>
+        <v>0.1878669891475093</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -7881,16 +7881,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.03630198133205593</v>
+        <v>-0.01372104411497332</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2404232492315805</v>
+        <v>0.2470907237720764</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2216358550385747</v>
+        <v>0.2162601209939226</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -7940,16 +7940,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.02578375031800799</v>
+        <v>0.0596357001910377</v>
       </c>
       <c r="O5" s="5">
         <v>12</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2588369814597283</v>
+        <v>0.2651665206528988</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2256130553531868</v>
+        <v>0.2225847698274729</v>
       </c>
       <c r="R5" s="5">
         <v>12</v>
@@ -8122,13 +8122,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05975699281128367</v>
+        <v>-0.06028988212767672</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1267793535232664</v>
+        <v>0.1267561844225537</v>
       </c>
       <c r="Q3" s="4">
         <v>0.1252885280237915</v>
@@ -8181,16 +8181,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.07958369198184116</v>
+        <v>-0.04677350338621977</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1299827963118711</v>
+        <v>0.1226290767798915</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1315868502370331</v>
+        <v>0.1235327764639126</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -8240,16 +8240,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.05303856095661862</v>
+        <v>-0.01162155660767894</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1358657423821825</v>
+        <v>0.137837980684513</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1166174775503386</v>
+        <v>0.1138563439270759</v>
       </c>
       <c r="R5" s="5">
         <v>15</v>
